--- a/config/summer_challenge/gates.xlsx
+++ b/config/summer_challenge/gates.xlsx
@@ -2679,14 +2679,14 @@
       </c>
       <c r="R15" s="1" t="inlineStr">
         <is>
+          <t>植物园</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>植物園</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>植物園</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>Botanical Garden</t>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果:潜伏取消のクールタイムなし;謝米は永久治癒禁止;その他味方の治癒率が大幅上昇する。\n勝利条件:謝米を撃破</t>
+          <t>关卡效果：没有潜伏取消的冷却时间；谢米永久禁止治愈；其他我方的治愈率大幅上升。\n胜利条件：击败谢米</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0x57D700#{0}の絵が書かれた#C0x5B545B##L1#の緑石板を獲得。</t>
+          <t>考验合格后，获得写有#L10##C0x57D700#{0}图案的#C0x5B545B##L1#绿石板。</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>かまくら</t>
+          <t>镰仓</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="W16" s="1" t="inlineStr">
         <is>
-          <t>ステージ効果：凍結目標は選択できず、味方全体が凍結され敗北する；敵は毎ターン制御率が上昇する。\n勝利条件：戦闘勝利</t>
+          <t>关卡效果：无法选择冻结目标，我方全体被冻结失败；敌人每回合控制率上升。\n胜利条件：战斗胜利</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0x00CED7#{0}の絵が書かれた#C0x5B545B##L1#の青石板を獲得。</t>
+          <t>试炼合格后，获得刻有#L10##C0x00CED7#{0}图案的#C0x5B545B##L1#青石板。</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>鏡の街</t>
+          <t>镜子之城</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="W17" s="1" t="inlineStr">
         <is>
-          <t>ステージ効果：対面の敵が鏡像となり、敵は鏡像目標の攻撃を受けて治癒を獲得する。\n勝利条件：戦闘勝利</t>
+          <t>关卡效果：对面的敌人变成镜像，敌人受到镜像目标的攻击获得治愈。\n胜利条件：战斗胜利</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0xAEAEA8#{0}の絵が書かれた#C0x5B545B##L1#の白色石板を獲得。</t>
+          <t>试炼合格后，获得印有#L10##C0xAEAEA8#{0}图案的#C0x5B545B##L1#白色石板。</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="R18" s="1" t="inlineStr">
         <is>
+          <t>火焰岛</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>火炎島</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>火炎島</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>Fire Island</t>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：噴火龍はそれぞれ異なる能力を持ち、生き残ろうと頑張っている！\n勝利条件：7ターン目開始時まで生存</t>
+          <t>关卡效果：每个喷火龙都拥有不同的能力，努力生存下去！\n胜利条件：生存至第7回合开始</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0xEE2417#{0}の絵が書かれた#C0x5B545B##L1#の赤石板を獲得。</t>
+          <t>试炼合格后，获得印有#L10##C0xEE2417#{0}图案的#C0x5B545B##L1#红石板。</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：胡地の本体は複数の分身に隠されているので、見つけ出しましょう！\n胡地は危険を察知すると本体を移動させます。\n勝利条件：{0}の本体を撃破</t>
+          <t>关卡效果：胡地的本体隐藏在多个分身中，快来发现吧！\n胡地察觉到危险的话会移动本体。\n胜利条件：击破{0}的本体</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0xC817EE#{0}の絵が書かれた#C0x5B545B##L1#の紫石板を獲得。</t>
+          <t>考验合格后，获得刻有#L10##C0xC817EE#{0}图案的#C0x5B545B##L1#紫石板。</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>観覧車</t>
+          <t>摩天轮</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：いたずら好きな胡帕はよく嘘をつく。本当のことを話す胡帕を見つけて手がかりを得ましょう。\n勝利条件：真実を話す胡帕を全員撃破</t>
+          <t>关卡效果：同调：喜欢恶作剧的胡帕经常说谎。找到能够说出真相的胡帕来获得线索吧。\n胜利条件：击溃了所有说真话的胡帕</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>試練に合格後、#L10##C0xEEE017#{0}の絵が書かれた#C0x5B545B##L1#の黄石板を獲得。</t>
+          <t>试炼合格后，获得刻有#L10##C0xEEE017#{0}图案的#C0x5B545B##L1#黄石板。</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：負傷した醜醜魚を守り抜きましょう。\n勝利条件：勝利し、醜醜魚が生存</t>
+          <t>关卡效果：保护受伤的丑鱼。\n胜利条件：胜利，丑丑鱼生存</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>不良少年を追い払った後、怪我をした{1}を助け、彼と友達になった。</t>
+          <t>赶走不良少年后，帮助受伤的{1}，并与他成为好友。</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>お宝埋蔵地</t>
+          <t>宝藏埋藏地</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="W22" s="1" t="inlineStr">
         <is>
-          <t>ステージ効果：色とりどりの柱が立ち並び、手に入れた石板と何らかの関係がありそうです。石板に描かれた模様は何を意味しているのか。\n勝利条件：ステージ勝利</t>
+          <t>关卡效果：五颜六色的柱子排列着，好像和到手的石板有什么关系。石板上描绘的图案意味着什么？\n胜利条件：关卡胜利</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>砂漠の謎を解いた後、精巧な{1}彫像を見つけた。</t>
+          <t>解开沙漠之谜后，发现了精美的{1}雕像。</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
-          <t>奪取</t>
+          <t>抢</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：美納斯の彫像を壊さないように注意しましょう。\n勝利条件：1ターン以内に勝利し、美納斯の彫像が破壊されない</t>
+          <t>关卡效果：注意不要破坏美纳斯雕像。\n胜利条件：1回合内胜利，美纳斯雕像不被破坏</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>{0}彫像は{0}一行に奪われてしまった。{1}彫像を取り戻す途中、あなたはうっかり飛行船に落ちてしまった……</t>
+          <t>{0}雕像被{0}一行人抢走了。{1}在取回雕像的途中，你不小心掉进了飞船里……</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>ステージ効果：美納斯の彫像を壊さないように注意しましょう。\n勝利条件：1ターン以内に勝利し、美納斯の彫像が無事</t>
+          <t>关卡效果：注意不要破坏美纳斯雕像。\n胜利条件：1回合内胜利，美纳斯雕像无事</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>{0}のおかげで、{1}を倒し、夏祭り探検イベントの最終勝利！</t>
+          <t>{0}，感谢{1}，打败夏日祭探险活动的最终胜利！</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
